--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104565_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104565_W12.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9921</v>
+        <v>5.5121</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2907</v>
+        <v>4.2182</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7013</v>
+        <v>1.294</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7294</v>
+        <v>2.7179</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8414</v>
+        <v>2.8296</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.112</v>
+        <v>-0.1117</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9569</v>
+        <v>3.9213</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1489</v>
+        <v>4.1229</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2275</v>
+        <v>-1.2034</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3553</v>
+        <v>1.8837</v>
       </c>
       <c r="T2" t="n">
-        <v>2.468</v>
+        <v>1.435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8873</v>
+        <v>0.4487</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0044</v>
+        <v>4.9734</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1905</v>
+        <v>1.9697</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8139</v>
+        <v>3.0037</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0144</v>
+        <v>1.9854</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8946</v>
+        <v>1.8928</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1197</v>
+        <v>0.0926</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6215</v>
+        <v>1.5663</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0536</v>
+        <v>2.0372</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4321</v>
+        <v>-0.471</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3929</v>
+        <v>0.4192</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6952</v>
+        <v>1.692</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5425</v>
+        <v>1.3838</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1527</v>
+        <v>0.3082</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4288</v>
+        <v>2.4646</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0214</v>
+        <v>0.8188</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4502</v>
+        <v>1.6458</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2502</v>
+        <v>-3.1775</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0924</v>
+        <v>-3.971</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.3426</v>
+        <v>0.7936</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.6535</v>
+        <v>-1.7464</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6682</v>
+        <v>-3.5108</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.3218</v>
+        <v>1.7644</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5967</v>
+        <v>-1.431</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4241</v>
+        <v>-0.4603</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0209</v>
+        <v>-0.9708</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3181</v>
+        <v>1.5039</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0858</v>
+        <v>0.931</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2323</v>
+        <v>0.5729</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7089</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8729</v>
+        <v>0.3841</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5819</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.1497</v>
+        <v>-1.0859</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.9519</v>
+        <v>0.4421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8023</v>
+        <v>-1.528</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6954</v>
+        <v>0.7467</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.4784</v>
+        <v>0.6722</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7831</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4543</v>
+        <v>-1.8326</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4735</v>
+        <v>-0.2301</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-1.6025</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2755</v>
+        <v>1.1578</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8166</v>
+        <v>0.7755</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5411</v>
+        <v>0.3823</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2519</v>
+        <v>0.9014</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2934</v>
+        <v>-0.6296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5453</v>
+        <v>1.531</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0967</v>
+        <v>-2.2587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4386</v>
+        <v>1.0887</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5353</v>
+        <v>-3.3474</v>
       </c>
       <c r="J6" t="n">
-        <v>0.75</v>
+        <v>-1.6734</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6754</v>
+        <v>0.6583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>-2.3317</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8467</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2368</v>
+        <v>0.4305</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6099</v>
+        <v>-1.0157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4413</v>
+        <v>0.7943</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>0.4991</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3505</v>
+        <v>0.2951</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2522</v>
+        <v>0.2142</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1914</v>
+        <v>1.7036</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0609</v>
+        <v>-1.4894</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7449</v>
+        <v>1.276</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1559</v>
+        <v>-0.5087</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5891</v>
+        <v>1.7847</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0173</v>
+        <v>0.7005</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>-0.5656</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2661</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7622</v>
+        <v>0.5755</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1732</v>
+        <v>0.0568</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5891</v>
+        <v>0.5187</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1878</v>
+        <v>1.0685</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>1.0031</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0209</v>
+        <v>0.0653</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2857</v>
+        <v>0.042</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2338</v>
+        <v>0.066</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5195</v>
+        <v>-0.024</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2654</v>
+        <v>-0.7419</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5152</v>
+        <v>-0.1551</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7806</v>
+        <v>-0.5868</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7075</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5612</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2688</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5578</v>
+        <v>-0.7592</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5118</v>
+        <v>-0.5868</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5928</v>
+        <v>0.101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5263</v>
+        <v>0.0487</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0665</v>
+        <v>0.0523</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3824</v>
+        <v>-0.2703</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.164</v>
+        <v>-0.1941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7816</v>
+        <v>-0.0762</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.042</v>
+        <v>0.9191</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1601</v>
+        <v>1.4507</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2021</v>
+        <v>-0.5316</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6771</v>
+        <v>2.4936</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>2.0544</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>0.4392</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3649</v>
+        <v>-1.5745</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1255</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.9708</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4745</v>
+        <v>0.8106</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4869</v>
+        <v>0.7268</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0124</v>
+        <v>0.0838</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9599</v>
+        <v>-0.4064</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7262</v>
+        <v>-1.1686</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2338</v>
+        <v>0.7622</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9203</v>
+        <v>-1.037</v>
       </c>
       <c r="H10" t="n">
-        <v>1.456</v>
+        <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5357</v>
+        <v>-1.2006</v>
       </c>
       <c r="J10" t="n">
-        <v>2.516</v>
+        <v>-0.6807</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0709</v>
+        <v>0.0345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4451</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5957</v>
+        <v>-0.3563</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6149</v>
+        <v>0.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9808</v>
+        <v>-0.4854</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1198</v>
+        <v>-0.5075</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1603</v>
+        <v>-0.4879</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0405</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.497</v>
+        <v>-1.2531</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8361</v>
+        <v>-2.6568</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3392</v>
+        <v>1.4037</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6157</v>
+        <v>-1.6172</v>
       </c>
       <c r="H11" t="n">
-        <v>2.212</v>
+        <v>2.2143</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8277</v>
+        <v>-3.8315</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.465</v>
+        <v>-0.4888</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0087</v>
+        <v>1.9995</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4737</v>
+        <v>-2.4883</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1507</v>
+        <v>-1.1284</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9826</v>
+        <v>1.2275</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6684</v>
+        <v>0.8823</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3142</v>
+        <v>0.3452</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.821</v>
+        <v>-2.3863</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8182</v>
+        <v>-3.7137</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0027</v>
+        <v>1.3274</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2794</v>
+        <v>-2.5752</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4775</v>
+        <v>0.3536</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8019</v>
+        <v>-2.9288</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8092</v>
+        <v>-2.0336</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1692</v>
+        <v>0.4547</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9784</v>
+        <v>-2.4883</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4702</v>
+        <v>-0.5416</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8236</v>
+        <v>-0.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5511</v>
+        <v>0.101</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2593</v>
+        <v>0.2808</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2918</v>
+        <v>-0.1797</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>0.3155</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7136</v>
+        <v>-2.9002</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8592</v>
+        <v>-1.7755</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1456</v>
+        <v>-1.1247</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5647</v>
+        <v>-2.289</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3594</v>
+        <v>-0.485</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9241</v>
+        <v>-1.804</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0031</v>
+        <v>-0.8435</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4707</v>
+        <v>0.1477</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4737</v>
+        <v>-0.9912</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5617</v>
+        <v>-1.4455</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1113</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4504</v>
+        <v>-0.8129</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2435</v>
+        <v>1.4783</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0907</v>
+        <v>1.3443</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3342</v>
+        <v>0.1339</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3214</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.474300000000003</v>
+        <v>7.873800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0678</v>
+        <v>-0.9778999999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>8.542100000000001</v>
+        <v>8.851800000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.813800000000001</v>
+        <v>-7.884</v>
       </c>
       <c r="H14" t="n">
-        <v>5.354000000000001</v>
+        <v>5.3155</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.1679</v>
+        <v>-13.1995</v>
       </c>
       <c r="J14" t="n">
-        <v>2.265900000000001</v>
+        <v>1.9792</v>
       </c>
       <c r="K14" t="n">
-        <v>8.277900000000001</v>
+        <v>8.122199999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.011800000000001</v>
+        <v>-6.143000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.0799</v>
+        <v>-9.863</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.924</v>
+        <v>-2.806700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.1562</v>
+        <v>-7.056500000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>9.073499999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6835</v>
+        <v>22.7633</v>
       </c>
       <c r="S14" t="n">
-        <v>9.874900000000002</v>
+        <v>11.3111</v>
       </c>
       <c r="T14" t="n">
-        <v>7.379800000000001</v>
+        <v>8.8225</v>
       </c>
       <c r="U14" t="n">
-        <v>2.495</v>
+        <v>2.4884</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.6599</v>
+        <v>-4.6586</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8962</v>
+        <v>1.8783</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.556</v>
+        <v>-6.536799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6592</v>
+        <v>5.5812</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8169</v>
+        <v>4.2696</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8423</v>
+        <v>1.3117</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3919</v>
+        <v>4.4068</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4384</v>
+        <v>1.4498</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9534</v>
+        <v>2.957</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7858</v>
+        <v>3.7704</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8334</v>
+        <v>2.8223</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6061</v>
+        <v>0.6365</v>
       </c>
       <c r="N15" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7327</v>
+        <v>-0.8256</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6079</v>
+        <v>-0.135</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1248</v>
+        <v>-0.6906</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4896</v>
+        <v>2.4275</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6676</v>
+        <v>2.4221</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.178</v>
+        <v>0.0054</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9566</v>
+        <v>1.9683</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1702</v>
+        <v>1.1787</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5719</v>
+        <v>1.5651</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3853</v>
+        <v>1.3789</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3847</v>
+        <v>0.4032</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1225</v>
+        <v>0.043</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3342</v>
+        <v>-0.1797</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3655</v>
+        <v>1.2701</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0579</v>
+        <v>-0.0733</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4234</v>
+        <v>1.3434</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6565</v>
+        <v>2.6599</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6248</v>
+        <v>-0.6233</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2813</v>
+        <v>3.2832</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6509</v>
+        <v>1.641</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4154</v>
+        <v>1.4214</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2743</v>
+        <v>-0.3703</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1534</v>
+        <v>-0.2494</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6541</v>
+        <v>1.1346</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7991</v>
+        <v>1.9948</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.145</v>
+        <v>-0.8602</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0088</v>
+        <v>3.0054</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3968</v>
+        <v>-2.3927</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4056</v>
+        <v>5.398</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4303</v>
+        <v>4.3968</v>
       </c>
       <c r="K18" t="n">
-        <v>0.107</v>
+        <v>0.0927</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3233</v>
+        <v>4.3041</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4215</v>
+        <v>-1.3915</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5038</v>
+        <v>-2.4854</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6991</v>
+        <v>-1.2171</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8166</v>
+        <v>-0.581</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8825</v>
+        <v>-0.6361</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0912</v>
+        <v>-0.3252</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5794</v>
+        <v>-1.6013</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6706</v>
+        <v>1.2761</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4434</v>
+        <v>-0.4244</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2624</v>
+        <v>1.2718</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7059</v>
+        <v>-1.6962</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.026</v>
+        <v>-1.048</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0232</v>
+        <v>-2.0338</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5825</v>
+        <v>0.6236</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2652</v>
+        <v>0.2861</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3174</v>
+        <v>0.3375</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.212</v>
+        <v>-0.6535</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0998</v>
+        <v>-0.098</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1122</v>
+        <v>-0.5556</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.857</v>
+        <v>-1.5353</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4524</v>
+        <v>-1.6873</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4046</v>
+        <v>0.1521</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5821</v>
+        <v>0.0789</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5368</v>
+        <v>-0.7673</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0453</v>
+        <v>0.8462</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.5476</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3952</v>
+        <v>-0.0624</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3413</v>
+        <v>0.61</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8457</v>
+        <v>-0.4687</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1416</v>
+        <v>-0.7048</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2959</v>
+        <v>0.2361</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9488</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5583</v>
+        <v>-2.0694</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5939</v>
+        <v>-0.6415</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0356</v>
+        <v>-1.4279</v>
       </c>
       <c r="V20" t="n">
-        <v>2.301</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5476</v>
+        <v>-1.7161</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2249</v>
+        <v>-2.7251</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6773</v>
+        <v>1.009</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0419</v>
+        <v>1.0489</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3781</v>
+        <v>0.3736</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6753</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1174</v>
+        <v>1.1375</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.8953</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1603</v>
+        <v>-0.3115</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8937</v>
+        <v>-0.5838</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3544</v>
+        <v>-2.1526</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1234</v>
+        <v>-1.9018</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.231</v>
+        <v>-0.2508</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.5796</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.775</v>
+        <v>-2.5334</v>
       </c>
       <c r="I22" t="n">
-        <v>0.845</v>
+        <v>-0.0462</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5774</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0488</v>
+        <v>-0.4072</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6263</v>
+        <v>-0.3505</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5074</v>
+        <v>-1.8219</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7261</v>
+        <v>-2.1262</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2187</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.5878</v>
+        <v>-2.9592</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.8781</v>
+        <v>-0.7341</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7651</v>
+        <v>-0.9149</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.2992</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.901</v>
+        <v>-2.7892</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9841</v>
+        <v>-2.7632</v>
       </c>
       <c r="F23" t="n">
-        <v>0.083</v>
+        <v>-0.026</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1537</v>
+        <v>-1.1473</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.482</v>
+        <v>-0.477</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6717</v>
+        <v>-0.6703</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9093</v>
+        <v>-0.9188</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2444</v>
+        <v>-0.2285</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5039</v>
+        <v>-0.3948</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0169</v>
+        <v>-0.1438</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0965</v>
+        <v>-3.0936</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.299</v>
+        <v>-2.3081</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7975</v>
+        <v>-0.7855</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8051</v>
+        <v>-1.7975</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1356</v>
+        <v>-2.1313</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3306</v>
+        <v>0.3338</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1453</v>
+        <v>-1.134</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6109</v>
+        <v>-0.6132</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3327</v>
+        <v>-0.3344</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9774</v>
+        <v>-4.4914</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1049</v>
+        <v>-4.478</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1275</v>
+        <v>-0.0134</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6726</v>
+        <v>0.6646</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2683</v>
+        <v>-0.2753</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9409</v>
+        <v>0.9399</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4705</v>
+        <v>1.4187</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4738</v>
+        <v>0.4439</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9967</v>
+        <v>0.9747</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7978</v>
+        <v>-0.7541</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0558</v>
+        <v>-0.0348</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.2172</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q25" t="n">
-        <v>-7.0318</v>
+        <v>-7.0566</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9112</v>
+        <v>-1.3969</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1825</v>
+        <v>-0.4743</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7286</v>
+        <v>-0.9226</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W25" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.474299999999999</v>
+        <v>-5.69</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.542400000000001</v>
+        <v>-8.851600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>2.068000000000001</v>
+        <v>3.1618</v>
       </c>
       <c r="G26" t="n">
-        <v>7.813999999999999</v>
+        <v>7.883999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.354</v>
+        <v>-5.315499999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>13.1679</v>
+        <v>13.1994</v>
       </c>
       <c r="J26" t="n">
-        <v>10.0799</v>
+        <v>9.863100000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9239</v>
+        <v>2.806800000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>7.156099999999999</v>
+        <v>7.0562</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2659</v>
+        <v>-1.979</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.277699999999999</v>
+        <v>-8.1221</v>
       </c>
       <c r="O26" t="n">
-        <v>6.011900000000001</v>
+        <v>6.143</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.1053</v>
       </c>
       <c r="Q26" t="n">
-        <v>-22.6833</v>
+        <v>-22.7633</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6102</v>
+        <v>13.6582</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.8748</v>
+        <v>-9.1272</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.495</v>
+        <v>-2.4884</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.379700000000001</v>
+        <v>-6.638799999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>4.659800000000001</v>
+        <v>4.6586</v>
       </c>
       <c r="W26" t="n">
-        <v>6.5561</v>
+        <v>6.536899999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.8963</v>
+        <v>-1.8783</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104565_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104565_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.536799999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104565_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-1.8783</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
